--- a/Bang_ke_hoach_SeqLogAD.xlsx
+++ b/Bang_ke_hoach_SeqLogAD.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive" sheetId="1" r:id="Rca0ed7ea34ab4e81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="2" r:id="Rfe3d0f62064b4620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Register" sheetId="3" r:id="R2fea86966c494e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates" sheetId="4" r:id="R5eadf0e5d3e94e11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="5" r:id="Ref9bff55e99a427e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Sources" sheetId="6" r:id="Rba03742a64b5491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Playbooks" sheetId="7" r:id="Rda01525c0f5d47c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive" sheetId="1" r:id="Ree30c6f621544082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="2" r:id="R2a7d16e6bb134123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Register" sheetId="3" r:id="Re8f97137e12648f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates" sheetId="4" r:id="Ra97768c796df4699"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="5" r:id="Rc7b80e9dc3e44426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Sources" sheetId="6" r:id="Rc7f94a147c1e453c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Playbooks" sheetId="7" r:id="R72fb88581e8948a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4908,7 +4908,7 @@
         <x:v>All required metadata resolved and reviewed under configs/models/base-freeze-v1.yaml; immutable revisions, policy/lock hashes and access evidence recorded. No placeholder permits PASS.</x:v>
       </x:c>
       <x:c r="K13" s="18" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Blocked</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="51.75" customHeight="1">
@@ -10358,7 +10358,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf47785bacb4746be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8883d4a3d6524594"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11917,7 +11917,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b42dfea0ff4772"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d191dd10e8d442e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Bang_ke_hoach_SeqLogAD.xlsx
+++ b/Bang_ke_hoach_SeqLogAD.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive" sheetId="1" r:id="Ree30c6f621544082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="2" r:id="R2a7d16e6bb134123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Register" sheetId="3" r:id="Re8f97137e12648f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates" sheetId="4" r:id="Ra97768c796df4699"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="5" r:id="Rc7b80e9dc3e44426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Sources" sheetId="6" r:id="Rc7f94a147c1e453c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Playbooks" sheetId="7" r:id="R72fb88581e8948a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive" sheetId="1" r:id="R1e08e2d1c99a4730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="2" r:id="Rab40ff8724614071"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Register" sheetId="3" r:id="Rd26e050d5c724817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gates" sheetId="4" r:id="R89735ed6ee794e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="5" r:id="R6066c9e3ce504e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Sources" sheetId="6" r:id="Rf10f86214efa4ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task Playbooks" sheetId="7" r:id="Rcb2aac62c2af404c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4908,7 +4908,7 @@
         <x:v>All required metadata resolved and reviewed under configs/models/base-freeze-v1.yaml; immutable revisions, policy/lock hashes and access evidence recorded. No placeholder permits PASS.</x:v>
       </x:c>
       <x:c r="K13" s="18" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="51.75" customHeight="1">
@@ -10358,7 +10358,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8883d4a3d6524594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R670bf6f9ac714a25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11917,7 +11917,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d191dd10e8d442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77446562a0ea4a5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>